--- a/LF/PreTAS/Zambia/sites.xlsx
+++ b/LF/PreTAS/Zambia/sites.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\LF\PreTAS\Zambia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA7FB45C-5002-4CF5-838B-1759E01286FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE135DD-AC9E-4D61-B76D-2E356A14BB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{152E16D4-4C4F-4A65-AC9A-06FA6A2E78B2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
   <si>
     <t>Sn</t>
   </si>
@@ -66,13 +66,16 @@
   </si>
   <si>
     <t>Choma Health Post</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,16 +83,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor theme="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -97,12 +114,90 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="7"/>
+      </right>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="7"/>
+      </right>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,19 +213,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3343A3E-497F-4998-9D8D-2533D48AFC90}" name="Table3" displayName="Table3" ref="A1:E3" totalsRowShown="0">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{71565037-6078-4C3B-903C-C88FEF0EBD0A}" name="Sn"/>
-    <tableColumn id="2" xr3:uid="{ADB6BC77-8FF7-462C-AD0E-0D1E4434EB07}" name="Province"/>
-    <tableColumn id="3" xr3:uid="{0B21DDE6-E083-4F8E-AD82-2AD0BB8AFDCE}" name="EU#"/>
-    <tableColumn id="4" xr3:uid="{FB522498-3378-482D-B08F-1E17DCE95415}" name="District"/>
-    <tableColumn id="5" xr3:uid="{9C9864B2-9088-45C1-BB43-0783890F8C86}" name="Sites/Community"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,64 +532,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBEB35A-BD24-44A3-8DD5-D7719D9BF150}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="10"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="F2">
+        <v>101</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.CONCAT(F2, "(", E2, ")")</f>
+        <v>101(Mulekatembo Rural Health Centre)</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="9" t="s">
         <v>9</v>
+      </c>
+      <c r="F3">
+        <v>102</v>
+      </c>
+      <c r="G3" t="str">
+        <f>_xlfn.CONCAT(F3, "(", E3, ")")</f>
+        <v>102(Choma Health Post)</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:L3">
+    <sortCondition ref="L2:L3"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>